--- a/web/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/web/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2019-02-17</t>
+          <t>2019-02-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-05-31</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2019-08-04</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2020-05-05</t>
+          <t>2020-05-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2019-11-10</t>
+          <t>2019-11-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2018-05-17</t>
+          <t>2018-05-18</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2019-07-08</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2018-08-21</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2018-07-22</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2018-02-08</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2019-07-31</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2020-01-06</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2019-03-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2018-08-26</t>
+          <t>2018-08-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2018-04-24</t>
+          <t>2018-04-25</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2018-08-27</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
+          <t>2019-10-11</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2018-06-14</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2018-05-03</t>
+          <t>2018-05-04</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2019-05-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2019-02-18</t>
+          <t>2019-02-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2018-06-11</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2018-06-14</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2018-02-13</t>
+          <t>2018-02-14</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2018-03-21</t>
+          <t>2018-03-22</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
+          <t>2018-10-26</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2019-07-31</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2018-06-06</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2018-02-02</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2018-03-26</t>
+          <t>2018-03-27</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2018-05-14</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2018-03-20</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2018-05-23</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2019-09-05</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2018-06-06</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2018-01-30</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2018-05-13</t>
+          <t>2018-05-14</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2018-02-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2019-05-29</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2018-02-14</t>
+          <t>2018-02-15</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2019-06-16</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2019-07-28</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
+          <t>2018-09-10</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2018-01-30</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2018-05-02</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2019-07-21</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2018-04-29</t>
+          <t>2018-04-30</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2019-07-12</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2018-10-11</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2018-01-30</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
+          <t>2018-04-13</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2018-03-20</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2019-06-29</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2018-01-03</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2018-03-08</t>
+          <t>2018-03-09</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2018-02-20</t>
+          <t>2018-02-21</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
+          <t>2019-10-04</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2019-03-25</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2019-07-14</t>
+          <t>2019-07-15</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2017-11-27</t>
+          <t>2017-11-28</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2018-01-09</t>
+          <t>2018-01-10</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2018-02-19</t>
+          <t>2018-02-20</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2018-02-05</t>
+          <t>2018-02-06</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
+          <t>2017-11-24</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2018-06-21</t>
+          <t>2018-06-22</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2017-12-14</t>
+          <t>2017-12-15</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2018-02-19</t>
+          <t>2018-02-20</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-05-30</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2020-03-15</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2018-01-16</t>
+          <t>2018-01-17</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-05-12</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2018-05-20</t>
+          <t>2018-05-21</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2018-01-18</t>
+          <t>2018-01-19</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2017-11-23</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2019-08-12</t>
+          <t>2019-08-13</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2019-02-19</t>
+          <t>2019-02-20</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2019-07-08</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>2020-03-27</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17743,7 +17743,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2018-04-08</t>
+          <t>2018-04-09</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2018-06-07</t>
+          <t>2018-06-08</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2017-12-27</t>
+          <t>2017-12-28</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2018-01-18</t>
+          <t>2018-01-19</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-05-12</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-05-12</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2018-03-20</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2018-05-25</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2018-06-14</t>
+          <t>2018-06-15</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2017-12-07</t>
+          <t>2017-12-08</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19355,7 +19355,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2017-12-13</t>
+          <t>2017-12-14</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19417,7 +19417,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2019-04-03</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2019-06-03</t>
+          <t>2019-06-04</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19913,7 +19913,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2017-12-12</t>
+          <t>2017-12-13</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-05-30</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2019-05-02</t>
+          <t>2019-05-03</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20657,7 +20657,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20719,7 +20719,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2018-02-25</t>
+          <t>2018-02-26</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2019-04-03</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2018-01-11</t>
+          <t>2018-01-12</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2018-07-20</t>
+          <t>2018-07-21</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019-05-10</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2019-01-17</t>
+          <t>2019-01-18</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2019-05-19</t>
+          <t>2019-05-20</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2018-05-20</t>
+          <t>2018-05-21</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2018-05-02</t>
+          <t>2018-05-03</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2018-05-20</t>
+          <t>2018-05-21</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2017-12-13</t>
+          <t>2017-12-14</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2017-12-07</t>
+          <t>2017-12-08</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2018-05-08</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2018-07-22</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2019-04-28</t>
+          <t>2019-04-29</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22455,7 +22455,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22703,7 +22703,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2018-04-27</t>
+          <t>2018-04-28</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23075,7 +23075,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2017-12-27</t>
+          <t>2017-12-28</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23261,7 +23261,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2019-04-09</t>
+          <t>2019-04-10</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2018-08-08</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23385,7 +23385,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2018-12-03</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23571,7 +23571,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23633,7 +23633,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23695,7 +23695,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2018-05-23</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
+          <t>2018-06-14</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24005,7 +24005,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2018-02-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2018-08-30</t>
+          <t>2018-08-31</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24501,7 +24501,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2018-07-22</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24873,7 +24873,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2019-03-14</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2019-04-07</t>
+          <t>2019-04-08</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25059,7 +25059,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25121,7 +25121,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2019-02-26</t>
+          <t>2019-02-27</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2018-08-27</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2018-08-08</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2018-10-02</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2019-05-20</t>
+          <t>2019-05-21</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25617,7 +25617,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2019-05-15</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2018-09-28</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2019-04-16</t>
+          <t>2019-04-17</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25927,7 +25927,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2019-02-11</t>
+          <t>2019-02-12</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -25989,7 +25989,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2017-12-10</t>
+          <t>2017-12-11</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2017-12-12</t>
+          <t>2017-12-13</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2018-04-10</t>
+          <t>2018-04-11</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2018-08-08</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2019-03-17</t>
+          <t>2019-03-18</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26547,7 +26547,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
+          <t>2019-05-31</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2018-05-27</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26733,7 +26733,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
+          <t>2018-09-26</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2019-01-22</t>
+          <t>2019-01-23</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2019-03-27</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-12-07</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2017-12-20</t>
+          <t>2017-12-21</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27105,7 +27105,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27167,7 +27167,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2018-03-20</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27229,7 +27229,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2019-04-11</t>
+          <t>2019-04-12</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27415,7 +27415,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2018-09-17</t>
+          <t>2018-09-18</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27477,7 +27477,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019-05-27</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2019-05-17</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2018-10-08</t>
+          <t>2018-10-09</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
+          <t>2018-10-05</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2019-04-02</t>
+          <t>2019-04-03</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27911,7 +27911,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2019-01-29</t>
+          <t>2019-01-30</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2017-12-14</t>
+          <t>2017-12-15</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2018-01-16</t>
+          <t>2018-01-17</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28097,7 +28097,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-03-06</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2018-02-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28221,7 +28221,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2018-08-08</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28345,7 +28345,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2019-04-23</t>
+          <t>2019-04-24</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2019-06-06</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2019-10-24</t>
+          <t>2019-10-25</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2019-08-11</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28903,7 +28903,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2019-07-28</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2019-10-24</t>
+          <t>2019-10-25</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2019-10-15</t>
+          <t>2019-10-16</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2020-01-08</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2019-12-05</t>
+          <t>2019-12-06</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
+          <t>2019-11-18</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29461,7 +29461,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29698,7 +29698,7 @@
           <t>A | 234呎 (开放式)
 $711万
 $30,396/呎
-(20年-05月-05日)</t>
+(20年-05月-06日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -29706,7 +29706,7 @@
           <t>B | 290呎 (1房)
 $897万
 $30,932/呎
-(20年-05月-19日)</t>
+(20年-05月-20日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -29714,7 +29714,7 @@
           <t>C | 293呎 (1房)
 $919万
 $31,368/呎
-(21年-05月-05日)</t>
+(21年-05月-06日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -29722,7 +29722,7 @@
           <t>D | 290呎 (1房)
 $868万
 $29,926/呎
-(20年-05月-26日)</t>
+(20年-05月-27日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -29730,7 +29730,7 @@
           <t>E | 299呎 (1房)
 $916万
 $30,630/呎
-(21年-07月-29日)</t>
+(21年-07月-30日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -29738,7 +29738,7 @@
           <t>F | 451呎 (2房)
 $1221万
 $27,066/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -29754,7 +29754,7 @@
           <t>H | 290呎 (1房)
 $820万
 $28,284/呎
-(19年-08月-04日)</t>
+(19年-08月-05日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -29762,7 +29762,7 @@
           <t>J | 219呎 (开放式)
 $626万
 $28,587/呎
-(18年-05月-31日)</t>
+(18年-06月-01日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -29770,7 +29770,7 @@
           <t>K | 293呎 (1房)
 $866万
 $29,560/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
       <c r="L5" s="20" t="inlineStr">
@@ -29778,7 +29778,7 @@
           <t>L | 297呎 (1房)
 $838万
 $28,225/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -29786,7 +29786,7 @@
           <t>M | 214呎 (开放式)
 $643万
 $30,046/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -29794,7 +29794,7 @@
           <t>N | 216呎 (开放式)
 $641万
 $29,666/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="O5" s="20" t="inlineStr">
@@ -29802,7 +29802,7 @@
           <t>P | 384呎 (2房)
 $736万
 $19,160/呎
-(19年-02月-17日)</t>
+(19年-02月-18日)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -29810,7 +29810,7 @@
           <t>Q | 299呎 (1房)
 $882万
 $29,488/呎
-(20年-02月-05日)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="Q5" s="20" t="inlineStr">
@@ -29818,7 +29818,7 @@
           <t>R | 238呎 (开放式)
 $722万
 $30,348/呎
-(21年-09月-28日)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -29833,7 +29833,7 @@
           <t>A | 234呎 (开放式)
 $706万
 $30,158/呎
-(19年-07月-07日)</t>
+(19年-07月-08日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -29841,7 +29841,7 @@
           <t>B | 290呎 (1房)
 $871万
 $30,043/呎
-(21年-05月-04日)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -29849,7 +29849,7 @@
           <t>C | 293呎 (1房)
 $884万
 $30,157/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -29857,7 +29857,7 @@
           <t>D | 290呎 (1房)
 $843万
 $29,070/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -29865,7 +29865,7 @@
           <t>E | 300呎 (1房)
 $890万
 $29,662/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -29873,7 +29873,7 @@
           <t>F | 451呎 (2房)
 $1210万
 $26,833/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -29889,7 +29889,7 @@
           <t>H | 290呎 (1房)
 $816万
 $28,127/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -29897,7 +29897,7 @@
           <t>J | 218呎 (开放式)
 $616万
 $28,273/呎
-(18年-05月-17日)</t>
+(18年-05月-18日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -29905,7 +29905,7 @@
           <t>K | 293呎 (1房)
 $835万
 $28,497/呎
-(21年-10月-04日)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -29913,7 +29913,7 @@
           <t>L | 297呎 (1房)
 $809万
 $27,230/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -29921,7 +29921,7 @@
           <t>M | 214呎 (开放式)
 $614万
 $28,669/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -29929,7 +29929,7 @@
           <t>N | 216呎 (开放式)
 $618万
 $28,606/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="O6" s="20" t="inlineStr">
@@ -29937,7 +29937,7 @@
           <t>P | 384呎 (2房)
 $1082万
 $28,190/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="P6" s="20" t="inlineStr">
@@ -29945,7 +29945,7 @@
           <t>Q | 299呎 (1房)
 $872万
 $29,155/呎
-(19年-11月-10日)</t>
+(19年-11月-11日)</t>
         </is>
       </c>
       <c r="Q6" s="20" t="inlineStr">
@@ -29953,7 +29953,7 @@
           <t>R | 238呎 (开放式)
 $716万
 $30,065/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -29968,7 +29968,7 @@
           <t>A | 234呎 (开放式)
 $697万
 $29,785/呎
-(19年-07月-31日)</t>
+(19年-08月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -29976,7 +29976,7 @@
           <t>B | 290呎 (1房)
 $869万
 $29,975/呎
-(20年-07月-16日)</t>
+(20年-07月-17日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -29984,7 +29984,7 @@
           <t>C | 293呎 (1房)
 $891万
 $30,411/呎
-(21年-06月-16日)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -29992,7 +29992,7 @@
           <t>D | 290呎 (1房)
 $793万
 $27,353/呎
-(18年-02月-07日)</t>
+(18年-02月-08日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -30000,7 +30000,7 @@
           <t>E | 300呎 (1房)
 $870万
 $29,004/呎
-(19年-03月-05日)</t>
+(19年-03月-06日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -30008,7 +30008,7 @@
           <t>F | 451呎 (2房)
 $1199万
 $26,576/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -30024,7 +30024,7 @@
           <t>H | 290呎 (1房)
 $799万
 $27,569/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -30032,7 +30032,7 @@
           <t>J | 219呎 (开放式)
 $623万
 $28,467/呎
-(18年-05月-09日)</t>
+(18年-05月-10日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -30040,7 +30040,7 @@
           <t>K | 293呎 (1房)
 $811万
 $27,673/呎
-(18年-07月-22日)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -30048,7 +30048,7 @@
           <t>L | 297呎 (1房)
 $801万
 $26,965/呎
-(18年-08月-21日)</t>
+(18年-08月-22日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -30056,7 +30056,7 @@
           <t>M | 214呎 (开放式)
 $614万
 $28,692/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -30064,7 +30064,7 @@
           <t>N | 216呎 (开放式)
 $618万
 $28,631/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr">
@@ -30072,7 +30072,7 @@
           <t>P | 384呎 (2房)
 $1061万
 $27,629/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
@@ -30080,7 +30080,7 @@
           <t>Q | 299呎 (1房)
 $867万
 $28,989/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="Q7" s="20" t="inlineStr">
@@ -30088,7 +30088,7 @@
           <t>R | 238呎 (开放式)
 $720万
 $30,240/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -30103,7 +30103,7 @@
           <t>A | 234呎 (开放式)
 $688万
 $29,411/呎
-(19年-07月-25日)</t>
+(19年-07月-26日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -30111,7 +30111,7 @@
           <t>B | 290呎 (1房)
 $849万
 $29,283/呎
-(20年-07月-02日)</t>
+(20年-07月-03日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -30119,7 +30119,7 @@
           <t>C | 293呎 (1房)
 $862万
 $29,408/呎
-(21年-06月-07日)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -30127,7 +30127,7 @@
           <t>D | 290呎 (1房)
 $814万
 $28,064/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -30135,7 +30135,7 @@
           <t>E | 299呎 (1房)
 $868万
 $29,044/呎
-(18年-08月-27日)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -30143,7 +30143,7 @@
           <t>F | 451呎 (2房)
 $1187万
 $26,318/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -30159,7 +30159,7 @@
           <t>H | 290呎 (1房)
 $783万
 $27,016/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -30167,7 +30167,7 @@
           <t>J | 219呎 (开放式)
 $611万
 $27,906/呎
-(18年-04月-24日)</t>
+(18年-04月-25日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -30175,7 +30175,7 @@
           <t>K | 293呎 (1房)
 $803万
 $27,411/呎
-(18年-08月-26日)</t>
+(18年-08月-27日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -30183,7 +30183,7 @@
           <t>L | 297呎 (1房)
 $793万
 $26,699/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -30191,7 +30191,7 @@
           <t>M | 214呎 (开放式)
 $608万
 $28,423/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -30199,7 +30199,7 @@
           <t>N | 216呎 (开放式)
 $606万
 $28,065/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -30207,7 +30207,7 @@
           <t>P | 384呎 (2房)
 $776万
 $20,215/呎
-(19年-03月-26日)</t>
+(19年-03月-27日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -30215,7 +30215,7 @@
           <t>Q | 299呎 (1房)
 $862万
 $28,824/呎
-(20年-01月-05日)</t>
+(20年-01月-06日)</t>
         </is>
       </c>
       <c r="Q8" s="20" t="inlineStr">
@@ -30223,7 +30223,7 @@
           <t>R | 238呎 (开放式)
 $724万
 $30,412/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -30238,7 +30238,7 @@
           <t>A | 234呎 (开放式)
 $675万
 $28,829/呎
-(19年-05月-06日)</t>
+(19年-05月-07日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -30246,7 +30246,7 @@
           <t>B | 290呎 (1房)
 $841万
 $28,998/呎
-(20年-05月-27日)</t>
+(20年-05月-28日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -30254,7 +30254,7 @@
           <t>C | 293呎 (1房)
 $853万
 $29,126/呎
-(21年-05月-27日)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30262,7 +30262,7 @@
           <t>D | 290呎 (1房)
 $823万
 $28,378/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -30270,7 +30270,7 @@
           <t>E | 300呎 (1房)
 $851万
 $28,376/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -30278,7 +30278,7 @@
           <t>F | 451呎 (2房)
 $1108万
 $24,579/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -30294,7 +30294,7 @@
           <t>H | 290呎 (1房)
 $786万
 $27,118/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -30302,7 +30302,7 @@
           <t>J | 219呎 (开放式)
 $601万
 $27,437/呎
-(18年-05月-03日)</t>
+(18年-05月-04日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -30310,7 +30310,7 @@
           <t>K | 293呎 (1房)
 $798万
 $27,232/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -30318,7 +30318,7 @@
           <t>L | 297呎 (1房)
 $796万
 $26,802/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -30326,7 +30326,7 @@
           <t>M | 214呎 (开放式)
 $611万
 $28,529/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -30334,7 +30334,7 @@
           <t>N | 216呎 (开放式)
 $609万
 $28,178/呎
-(18年-06月-14日)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -30342,7 +30342,7 @@
           <t>P | 384呎 (2房)
 $1065万
 $27,726/呎
-(19年-04月-07日)</t>
+(19年-04月-08日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -30350,7 +30350,7 @@
           <t>Q | 299呎 (1房)
 $866万
 $28,961/呎
-(19年-10月-10日)</t>
+(19年-10月-11日)</t>
         </is>
       </c>
       <c r="Q9" s="21" t="inlineStr">
@@ -30373,7 +30373,7 @@
           <t>A | 234呎 (开放式)
 $668万
 $28,553/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -30381,7 +30381,7 @@
           <t>B | 290呎 (1房)
 $841万
 $29,015/呎
-(19年-07月-18日)</t>
+(19年-07月-19日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -30389,7 +30389,7 @@
           <t>C | 293呎 (1房)
 $845万
 $28,844/呎
-(20年-07月-20日)</t>
+(20年-07月-21日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -30397,7 +30397,7 @@
           <t>D | 290呎 (1房)
 $815万
 $28,103/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -30405,7 +30405,7 @@
           <t>E | 300呎 (1房)
 $852万
 $28,403/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -30413,7 +30413,7 @@
           <t>F | 451呎 (2房)
 $1171万
 $25,973/呎
-(18年-05月-15日)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -30429,7 +30429,7 @@
           <t>H | 290呎 (1房)
 $781万
 $26,943/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -30437,7 +30437,7 @@
           <t>J | 219呎 (开放式)
 $569万
 $25,967/呎
-(18年-02月-13日)</t>
+(18年-02月-14日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -30445,7 +30445,7 @@
           <t>K | 293呎 (1房)
 $801万
 $27,339/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -30453,7 +30453,7 @@
           <t>L | 297呎 (1房)
 $782万
 $26,344/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -30461,7 +30461,7 @@
           <t>M | 214呎 (开放式)
 $600万
 $28,051/呎
-(18年-06月-14日)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -30469,7 +30469,7 @@
           <t>N | 216呎 (开放式)
 $598万
 $27,704/呎
-(18年-06月-11日)</t>
+(18年-06月-12日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -30477,7 +30477,7 @@
           <t>P | 384呎 (2房)
 $1088万
 $28,344/呎
-(19年-02月-18日)</t>
+(19年-02月-19日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -30485,7 +30485,7 @@
           <t>Q | 299呎 (1房)
 $852万
 $28,494/呎
-(19年-08月-28日)</t>
+(19年-08月-29日)</t>
         </is>
       </c>
       <c r="Q10" s="21" t="inlineStr">
@@ -30508,7 +30508,7 @@
           <t>A | 234呎 (开放式)
 $669万
 $28,570/呎
-(18年-10月-25日)</t>
+(18年-10月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -30516,7 +30516,7 @@
           <t>B | 290呎 (1房)
 $824万
 $28,428/呎
-(20年-04月-08日)</t>
+(20年-04月-09日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -30524,7 +30524,7 @@
           <t>C | 293呎 (1房)
 $837万
 $28,562/呎
-(20年-05月-28日)</t>
+(20年-05月-29日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30532,7 +30532,7 @@
           <t>D | 290呎 (1房)
 $799万
 $27,542/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -30540,7 +30540,7 @@
           <t>E | 300呎 (1房)
 $844万
 $28,128/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -30548,7 +30548,7 @@
           <t>F | 451呎 (2房)
 $1151万
 $25,530/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -30556,7 +30556,7 @@
           <t>G | 301呎 (1房)
 $827万
 $27,489/呎
-(21年-05月-10日)</t>
+(21年-05月-11日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -30564,7 +30564,7 @@
           <t>H | 290呎 (1房)
 $776万
 $26,761/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -30572,7 +30572,7 @@
           <t>J | 219呎 (开放式)
 $593万
 $27,086/呎
-(18年-03月-21日)</t>
+(18年-03月-22日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -30580,7 +30580,7 @@
           <t>K | 293呎 (1房)
 $796万
 $27,162/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -30588,7 +30588,7 @@
           <t>L | 297呎 (1房)
 $785万
 $26,444/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -30596,7 +30596,7 @@
           <t>M | 214呎 (开放式)
 $573万
 $26,773/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -30604,7 +30604,7 @@
           <t>N | 216呎 (开放式)
 $601万
 $27,813/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -30612,7 +30612,7 @@
           <t>P | 384呎 (2房)
 $1041万
 $27,105/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -30620,7 +30620,7 @@
           <t>Q | 299呎 (1房)
 $844万
 $28,217/呎
-(19年-09月-03日)</t>
+(19年-09月-04日)</t>
         </is>
       </c>
       <c r="Q11" s="21" t="inlineStr">
@@ -30643,7 +30643,7 @@
           <t>A | 234呎 (开放式)
 $662万
 $28,291/呎
-(18年-08月-12日)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -30651,7 +30651,7 @@
           <t>B | 290呎 (1房)
 $825万
 $28,442/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -30659,7 +30659,7 @@
           <t>C | 293呎 (1房)
 $829万
 $28,280/呎
-(20年-05月-21日)</t>
+(20年-05月-22日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -30667,7 +30667,7 @@
           <t>D | 290呎 (1房)
 $753万
 $25,973/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -30675,7 +30675,7 @@
           <t>E | 300呎 (1房)
 $796万
 $26,528/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -30683,7 +30683,7 @@
           <t>F | 451呎 (2房)
 $1168万
 $25,893/呎
-(18年-05月-14日)</t>
+(18年-05月-15日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -30691,7 +30691,7 @@
           <t>G | 301呎 (1房)
 $813万
 $27,020/呎
-(19年-09月-03日)</t>
+(19年-09月-04日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -30699,7 +30699,7 @@
           <t>H | 290呎 (1房)
 $763万
 $26,305/呎
-(18年-03月-26日)</t>
+(18年-03月-27日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -30707,7 +30707,7 @@
           <t>J | 219呎 (开放式)
 $567万
 $25,898/呎
-(18年-02月-01日)</t>
+(18年-02月-02日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -30715,7 +30715,7 @@
           <t>K | 293呎 (1房)
 $791万
 $26,982/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -30723,7 +30723,7 @@
           <t>L | 297呎 (1房)
 $772万
 $25,992/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -30731,7 +30731,7 @@
           <t>M | 214呎 (开放式)
 $587万
 $27,440/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -30739,7 +30739,7 @@
           <t>N | 216呎 (开放式)
 $609万
 $28,207/呎
-(18年-06月-06日)</t>
+(18年-06月-07日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -30747,7 +30747,7 @@
           <t>P | 384呎 (2房)
 $1034万
 $26,925/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -30755,7 +30755,7 @@
           <t>Q | 299呎 (1房)
 $844万
 $28,235/呎
-(19年-07月-31日)</t>
+(19年-08月-01日)</t>
         </is>
       </c>
       <c r="Q12" s="20" t="inlineStr">
@@ -30763,7 +30763,7 @@
           <t>R | 238呎 (开放式)
 $689万
 $28,935/呎
-(21年-01月-21日)</t>
+(21年-01月-22日)</t>
         </is>
       </c>
     </row>
@@ -30778,7 +30778,7 @@
           <t>A | 234呎 (开放式)
 $655万
 $28,012/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -30786,7 +30786,7 @@
           <t>B | 290呎 (1房)
 $808万
 $27,861/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -30794,7 +30794,7 @@
           <t>C | 293呎 (1房)
 $820万
 $28,001/呎
-(19年-07月-18日)</t>
+(19年-07月-19日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -30802,7 +30802,7 @@
           <t>D | 290呎 (1房)
 $799万
 $27,562/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -30810,7 +30810,7 @@
           <t>E | 299呎 (1房)
 $836万
 $27,961/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -30818,7 +30818,7 @@
           <t>F | 451呎 (2房)
 $1148万
 $25,454/呎
-(18年-04月-18日)</t>
+(18年-04月-19日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -30826,7 +30826,7 @@
           <t>G | 301呎 (1房)
 $808万
 $26,837/呎
-(20年-03月-11日)</t>
+(20年-03月-12日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -30834,7 +30834,7 @@
           <t>H | 290呎 (1房)
 $766万
 $26,403/呎
-(18年-05月-23日)</t>
+(18年-05月-24日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -30842,7 +30842,7 @@
           <t>J | 219呎 (开放式)
 $586万
 $26,739/呎
-(18年-03月-19日)</t>
+(18年-03月-20日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -30850,7 +30850,7 @@
           <t>K | 293呎 (1房)
 $794万
 $27,084/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -30858,7 +30858,7 @@
           <t>L | 297呎 (1房)
 $767万
 $25,816/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -30866,7 +30866,7 @@
           <t>M | 214呎 (开放式)
 $583万
 $27,257/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -30874,7 +30874,7 @@
           <t>N | 216呎 (开放式)
 $605万
 $28,021/呎
-(18年-06月-03日)</t>
+(18年-06月-04日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -30882,7 +30882,7 @@
           <t>P | 384呎 (2房)
 $1048万
 $27,280/呎
-(19年-04月-07日)</t>
+(19年-04月-08日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -30890,7 +30890,7 @@
           <t>Q | 299呎 (1房)
 $836万
 $27,956/呎
-(19年-07月-18日)</t>
+(19年-07月-19日)</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr">
@@ -30898,7 +30898,7 @@
           <t>R | 238呎 (开放式)
 $696万
 $29,259/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -30913,7 +30913,7 @@
           <t>A | 234呎 (开放式)
 $664万
 $28,382/呎
-(19年-07月-28日)</t>
+(19年-07月-29日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -30921,7 +30921,7 @@
           <t>B | 290呎 (1房)
 $811万
 $27,962/呎
-(19年-06月-16日)</t>
+(19年-06月-17日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -30929,7 +30929,7 @@
           <t>C | 293呎 (1房)
 $823万
 $28,105/呎
-(19年-07月-01日)</t>
+(19年-07月-02日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -30937,7 +30937,7 @@
           <t>D | 290呎 (1房)
 $778万
 $26,820/呎
-(18年-02月-14日)</t>
+(18年-02月-15日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -30945,7 +30945,7 @@
           <t>E | 300呎 (1房)
 $813万
 $27,113/呎
-(19年-05月-28日)</t>
+(19年-05月-29日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -30953,7 +30953,7 @@
           <t>F | 451呎 (2房)
 $1075万
 $23,828/呎
-(18年-02月-11日)</t>
+(18年-02月-12日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -30961,7 +30961,7 @@
           <t>G | 301呎 (1房)
 $811万
 $26,937/呎
-(19年-07月-17日)</t>
+(19年-07月-18日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -30969,7 +30969,7 @@
           <t>H | 290呎 (1房)
 $753万
 $25,951/呎
-(18年-05月-13日)</t>
+(18年-05月-14日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -30977,7 +30977,7 @@
           <t>J | 218呎 (开放式)
 $560万
 $25,678/呎
-(18年-01月-30日)</t>
+(18年-01月-31日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -30985,7 +30985,7 @@
           <t>K | 293呎 (1房)
 $772万
 $26,347/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -30993,7 +30993,7 @@
           <t>L | 297呎 (1房)
 $785万
 $26,447/呎
-(18年-06月-06日)</t>
+(18年-06月-07日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -31001,7 +31001,7 @@
           <t>M | 214呎 (开放式)
 $562万
 $26,245/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -31009,7 +31009,7 @@
           <t>N | 216呎 (开放式)
 $583万
 $26,987/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -31017,7 +31017,7 @@
           <t>P | 384呎 (2房)
 $1009万
 $26,288/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -31025,7 +31025,7 @@
           <t>Q | 299呎 (1房)
 $822万
 $27,480/呎
-(19年-09月-04日)</t>
+(19年-09月-05日)</t>
         </is>
       </c>
       <c r="Q14" s="20" t="inlineStr">
@@ -31033,7 +31033,7 @@
           <t>R | 238呎 (开放式)
 $685万
 $28,764/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -31048,7 +31048,7 @@
           <t>A | 234呎 (开放式)
 $647万
 $27,639/呎
-(18年-08月-12日)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -31056,7 +31056,7 @@
           <t>B | 290呎 (1房)
 $797万
 $27,481/呎
-(18年-10月-10日)</t>
+(18年-10月-11日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -31064,7 +31064,7 @@
           <t>C | 293呎 (1房)
 $809万
 $27,625/呎
-(19年-07月-11日)</t>
+(19年-07月-12日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -31072,7 +31072,7 @@
           <t>D | 290呎 (1房)
 $728万
 $25,106/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -31080,7 +31080,7 @@
           <t>E | 299呎 (1房)
 $816万
 $27,307/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -31088,7 +31088,7 @@
           <t>F | 451呎 (2房)
 $1121万
 $24,850/呎
-(18年-04月-29日)</t>
+(18年-04月-30日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -31096,7 +31096,7 @@
           <t>G | 301呎 (1房)
 $805万
 $26,752/呎
-(19年-07月-21日)</t>
+(19年-07月-22日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -31104,7 +31104,7 @@
           <t>H | 290呎 (1房)
 $747万
 $25,774/呎
-(18年-05月-01日)</t>
+(18年-05月-02日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -31112,7 +31112,7 @@
           <t>J | 218呎 (开放式)
 $562万
 $25,776/呎
-(18年-01月-30日)</t>
+(18年-01月-31日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -31120,7 +31120,7 @@
           <t>K | 293呎 (1房)
 $775万
 $26,448/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -31128,7 +31128,7 @@
           <t>L | 297呎 (1房)
 $756万
 $25,461/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -31136,7 +31136,7 @@
           <t>M | 214呎 (开放式)
 $564万
 $26,342/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -31144,7 +31144,7 @@
           <t>N | 216呎 (开放式)
 $585万
 $27,089/呎
-(18年-06月-03日)</t>
+(18年-06月-04日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>P | 384呎 (2房)
 $1013万
 $26,385/呎
-(18年-09月-09日)</t>
+(18年-09月-10日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -31160,7 +31160,7 @@
           <t>Q | 299呎 (1房)
 $816万
 $27,299/呎
-(19年-07月-25日)</t>
+(19年-07月-26日)</t>
         </is>
       </c>
       <c r="Q15" s="20" t="inlineStr">
@@ -31168,7 +31168,7 @@
           <t>R | 238呎 (开放式)
 $673万
 $28,276/呎
-(20年-05月-17日)</t>
+(20年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -31183,7 +31183,7 @@
           <t>A | 234呎 (开放式)
 $642万
 $27,450/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -31191,7 +31191,7 @@
           <t>B | 290呎 (1房)
 $800万
 $27,578/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -31199,7 +31199,7 @@
           <t>C | 293呎 (1房)
 $804万
 $27,437/呎
-(19年-06月-28日)</t>
+(19年-06月-29日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -31207,7 +31207,7 @@
           <t>D | 290呎 (1房)
 $731万
 $25,198/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31215,7 +31215,7 @@
           <t>E | 299呎 (1房)
 $803万
 $26,841/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31223,7 +31223,7 @@
           <t>F | 451呎 (2房)
 $1125万
 $24,939/呎
-(18年-03月-19日)</t>
+(18年-03月-20日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -31231,7 +31231,7 @@
           <t>G | 301呎 (1房)
 $791万
 $26,291/呎
-(20年-06月-07日)</t>
+(20年-06月-08日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -31239,7 +31239,7 @@
           <t>H | 290呎 (1房)
 $750万
 $25,867/呎
-(18年-04月-12日)</t>
+(18年-04月-13日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -31247,7 +31247,7 @@
           <t>J | 219呎 (开放式)
 $552万
 $25,223/呎
-(18年-01月-30日)</t>
+(18年-01月-31日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -31255,7 +31255,7 @@
           <t>K | 293呎 (1房)
 $770万
 $26,267/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -31263,7 +31263,7 @@
           <t>L | 297呎 (1房)
 $759万
 $25,552/呎
-(18年-06月-04日)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -31271,7 +31271,7 @@
           <t>M | 214呎 (开放式)
 $560万
 $26,162/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -31279,7 +31279,7 @@
           <t>N | 216呎 (开放式)
 $575万
 $26,626/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -31287,7 +31287,7 @@
           <t>P | 384呎 (2房)
 $1027万
 $26,748/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -31295,7 +31295,7 @@
           <t>Q | 299呎 (1房)
 $819万
 $27,400/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr">
@@ -31303,7 +31303,7 @@
           <t>R | 238呎 (开放式)
 $669万
 $28,089/呎
-(21年-05月-17日)</t>
+(21年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
           <t>A | 234呎 (开放式)
 $645万
 $27,550/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31326,7 +31326,7 @@
           <t>B | 290呎 (1房)
 $786万
 $27,101/呎
-(19年-03月-25日)</t>
+(19年-03月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -31334,7 +31334,7 @@
           <t>C | 293呎 (1房)
 $798万
 $27,248/呎
-(19年-10月-03日)</t>
+(19年-10月-04日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -31342,7 +31342,7 @@
           <t>D | 290呎 (1房)
 $718万
 $24,762/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31350,7 +31350,7 @@
           <t>E | 300呎 (1房)
 $806万
 $26,854/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31358,7 +31358,7 @@
           <t>F | 451呎 (2房)
 $1117万
 $24,766/呎
-(18年-02月-20日)</t>
+(18年-02月-21日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -31366,7 +31366,7 @@
           <t>G | 301呎 (1房)
 $794万
 $26,382/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -31374,7 +31374,7 @@
           <t>H | 290呎 (1房)
 $745万
 $25,688/呎
-(18年-03月-08日)</t>
+(18年-03月-09日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -31382,7 +31382,7 @@
           <t>J | 219呎 (开放式)
 $543万
 $24,791/呎
-(18年-01月-02日)</t>
+(18年-01月-03日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -31390,7 +31390,7 @@
           <t>K | 293呎 (1房)
 $780万
 $26,631/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -31398,7 +31398,7 @@
           <t>L | 297呎 (1房)
 $746万
 $25,109/呎
-(18年-05月-30日)</t>
+(18年-05月-31日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -31406,7 +31406,7 @@
           <t>M | 214呎 (开放式)
 $562万
 $26,258/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -31414,7 +31414,7 @@
           <t>N | 216呎 (开放式)
 $577万
 $26,724/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -31422,7 +31422,7 @@
           <t>P | 384呎 (2房)
 $999万
 $26,025/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -31430,7 +31430,7 @@
           <t>Q | 299呎 (1房)
 $808万
 $27,028/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr">
@@ -31438,7 +31438,7 @@
           <t>R | 238呎 (开放式)
 $660万
 $27,714/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -31453,7 +31453,7 @@
           <t>A | 234呎 (开放式)
 $634万
 $27,081/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -31461,7 +31461,7 @@
           <t>B | 290呎 (1房)
 $789万
 $27,194/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -31469,7 +31469,7 @@
           <t>C | 293呎 (1房)
 $801万
 $27,345/呎
-(19年-08月-15日)</t>
+(19年-08月-16日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31477,7 +31477,7 @@
           <t>D | 290呎 (1房)
 $713万
 $24,592/呎
-(17年-11月-23日)</t>
+(17年-11月-24日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31485,7 +31485,7 @@
           <t>E | 300呎 (1房)
 $762万
 $25,402/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31493,7 +31493,7 @@
           <t>F | 451呎 (2房)
 $1045万
 $23,179/呎
-(18年-02月-05日)</t>
+(18年-02月-06日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -31501,7 +31501,7 @@
           <t>G | 301呎 (1房)
 $789万
 $26,197/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -31509,7 +31509,7 @@
           <t>H | 290呎 (1房)
 $740万
 $25,510/呎
-(18年-02月-19日)</t>
+(18年-02月-20日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -31517,7 +31517,7 @@
           <t>J | 219呎 (开放式)
 $551万
 $25,145/呎
-(18年-01月-09日)</t>
+(18年-01月-10日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -31525,7 +31525,7 @@
           <t>K | 293呎 (1房)
 $775万
 $26,450/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -31533,7 +31533,7 @@
           <t>L | 297呎 (1房)
 $756万
 $25,455/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -31541,7 +31541,7 @@
           <t>M | 214呎 (开放式)
 $547万
 $25,539/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -31549,7 +31549,7 @@
           <t>N | 216呎 (开放式)
 $579万
 $26,819/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -31557,7 +31557,7 @@
           <t>P | 384呎 (2房)
 $945万
 $24,612/呎
-(17年-11月-27日)</t>
+(17年-11月-28日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -31565,7 +31565,7 @@
           <t>Q | 299呎 (1房)
 $789万
 $26,378/呎
-(19年-07月-14日)</t>
+(19年-07月-15日)</t>
         </is>
       </c>
       <c r="Q18" s="20" t="inlineStr">
@@ -31573,7 +31573,7 @@
           <t>R | 238呎 (开放式)
 $651万
 $27,338/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -31588,7 +31588,7 @@
           <t>A | 234呎 (开放式)
 $629万
 $26,892/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -31596,7 +31596,7 @@
           <t>B | 290呎 (1房)
 $783万
 $27,002/呎
-(19年-04月-14日)</t>
+(19年-04月-15日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -31604,7 +31604,7 @@
           <t>C | 293呎 (1房)
 $787万
 $26,872/呎
-(19年-05月-29日)</t>
+(19年-05月-30日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -31612,7 +31612,7 @@
           <t>D | 290呎 (1房)
 $716万
 $24,679/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31620,7 +31620,7 @@
           <t>E | 300呎 (1房)
 $757万
 $25,229/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31628,7 +31628,7 @@
           <t>F | 451呎 (2房)
 $1038万
 $23,015/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -31636,7 +31636,7 @@
           <t>G | 301呎 (1房)
 $783万
 $26,012/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -31644,7 +31644,7 @@
           <t>H | 290呎 (1房)
 $750万
 $25,855/呎
-(18年-02月-19日)</t>
+(18年-02月-20日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -31652,7 +31652,7 @@
           <t>J | 218呎 (开放式)
 $536万
 $24,569/呎
-(17年-12月-14日)</t>
+(17年-12月-15日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -31660,7 +31660,7 @@
           <t>K | 293呎 (1房)
 $746万
 $25,462/呎
-(18年-06月-21日)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -31668,7 +31668,7 @@
           <t>L | 297呎 (1房)
 $743万
 $25,015/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -31676,7 +31676,7 @@
           <t>M | 214呎 (开放式)
 $548万
 $25,628/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -31684,7 +31684,7 @@
           <t>N | 216呎 (开放式)
 $563万
 $26,085/呎
-(18年-05月-15日)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -31692,7 +31692,7 @@
           <t>P | 384呎 (2房)
 $985万
 $25,662/呎
-(18年-05月-16日)</t>
+(18年-05月-17日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -31700,7 +31700,7 @@
           <t>Q | 299呎 (1房)
 $791万
 $26,469/呎
-(19年-06月-02日)</t>
+(19年-06月-03日)</t>
         </is>
       </c>
       <c r="Q19" s="20" t="inlineStr">
@@ -31708,7 +31708,7 @@
           <t>R | 238呎 (开放式)
 $646万
 $27,147/呎
-(19年-06月-02日)</t>
+(19年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -31723,7 +31723,7 @@
           <t>A | 234呎 (开放式)
 $625万
 $26,708/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -31731,7 +31731,7 @@
           <t>B | 290呎 (1房)
 $778万
 $26,810/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -31739,7 +31739,7 @@
           <t>C | 293呎 (1房)
 $782万
 $26,684/呎
-(19年-05月-11日)</t>
+(19年-05月-12日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -31747,7 +31747,7 @@
           <t>D | 290呎 (1房)
 $725万
 $25,017/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31755,7 +31755,7 @@
           <t>E | 300呎 (1房)
 $752万
 $25,053/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -31763,7 +31763,7 @@
           <t>F | 451呎 (2房)
 $1063万
 $23,574/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -31771,7 +31771,7 @@
           <t>G | 301呎 (1房)
 $777万
 $25,828/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -31779,7 +31779,7 @@
           <t>H | 290呎 (1房)
 $687万
 $23,704/呎
-(18年-01月-16日)</t>
+(18年-01月-17日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -31787,7 +31787,7 @@
           <t>J | 219呎 (开放式)
 $538万
 $24,544/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -31795,7 +31795,7 @@
           <t>K | 293呎 (1房)
 $749万
 $25,553/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -31803,7 +31803,7 @@
           <t>L | 297呎 (1房)
 $738万
 $24,837/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -31811,7 +31811,7 @@
           <t>M | 214呎 (开放式)
 $545万
 $25,449/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -31819,7 +31819,7 @@
           <t>N | 216呎 (开放式)
 $565万
 $26,178/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -31827,7 +31827,7 @@
           <t>P | 384呎 (2房)
 $968万
 $25,215/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -31835,7 +31835,7 @@
           <t>Q | 299呎 (1房)
 $786万
 $26,283/呎
-(20年-03月-15日)</t>
+(20年-03月-16日)</t>
         </is>
       </c>
       <c r="Q20" s="20" t="inlineStr">
@@ -31843,7 +31843,7 @@
           <t>R | 238呎 (开放式)
 $648万
 $27,243/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -31858,7 +31858,7 @@
           <t>A | 234呎 (开放式)
 $616万
 $26,336/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -31866,7 +31866,7 @@
           <t>B | 290呎 (1房)
 $775万
 $26,718/呎
-(19年-02月-19日)</t>
+(19年-02月-20日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -31874,7 +31874,7 @@
           <t>C | 293呎 (1房)
 $787万
 $26,870/呎
-(19年-08月-12日)</t>
+(19年-08月-13日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -31882,7 +31882,7 @@
           <t>D | 290呎 (1房)
 $701万
 $24,166/呎
-(17年-11月-22日)</t>
+(17年-11月-23日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -31890,7 +31890,7 @@
           <t>E | 300呎 (1房)
 $778万
 $25,941/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -31898,7 +31898,7 @@
           <t>F | 451呎 (2房)
 $1038万
 $23,012/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -31906,7 +31906,7 @@
           <t>G | 301呎 (1房)
 $767万
 $25,467/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -31914,7 +31914,7 @@
           <t>H | 290呎 (1房)
 $692万
 $23,868/呎
-(18年-01月-18日)</t>
+(18年-01月-19日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -31922,7 +31922,7 @@
           <t>J | 218呎 (开放式)
 $541万
 $24,828/呎
-(17年-12月-06日)</t>
+(17年-12月-07日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -31930,7 +31930,7 @@
           <t>K | 293呎 (1房)
 $746万
 $25,461/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -31938,7 +31938,7 @@
           <t>L | 297呎 (1房)
 $735万
 $24,747/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -31946,7 +31946,7 @@
           <t>M | 214呎 (开放式)
 $537万
 $25,095/呎
-(18年-05月-20日)</t>
+(18年-05月-21日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -31954,7 +31954,7 @@
           <t>N | 216呎 (开放式)
 $564万
 $26,089/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -31962,7 +31962,7 @@
           <t>P | 384呎 (2房)
 $948万
 $24,686/呎
-(17年-12月-06日)</t>
+(17年-12月-07日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -31970,7 +31970,7 @@
           <t>Q | 299呎 (1房)
 $775万
 $25,917/呎
-(19年-05月-22日)</t>
+(19年-05月-23日)</t>
         </is>
       </c>
       <c r="Q21" s="20" t="inlineStr">
@@ -31978,7 +31978,7 @@
           <t>R | 238呎 (开放式)
 $639万
 $26,867/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -31993,7 +31993,7 @@
           <t>A | 234呎 (开放式)
 $612万
 $26,149/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32001,7 +32001,7 @@
           <t>B | 290呎 (1房)
 $769万
 $26,526/呎
-(19年-05月-23日)</t>
+(19年-05月-24日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -32009,7 +32009,7 @@
           <t>C | 293呎 (1房)
 $782万
 $26,680/呎
-(19年-08月-15日)</t>
+(19年-08月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -32017,7 +32017,7 @@
           <t>D | 290呎 (1房)
 $703万
 $24,248/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -32025,7 +32025,7 @@
           <t>E | 300呎 (1房)
 $744万
 $24,794/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -32033,7 +32033,7 @@
           <t>F | 451呎 (2房)
 $1030万
 $22,848/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -32041,7 +32041,7 @@
           <t>G | 301呎 (1房)
 $761万
 $25,284/呎
-(19年-05月-11日)</t>
+(19年-05月-12日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -32049,7 +32049,7 @@
           <t>H | 290呎 (1房)
 $680万
 $23,449/呎
-(18年-01月-18日)</t>
+(18年-01月-19日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -32057,7 +32057,7 @@
           <t>J | 219呎 (开放式)
 $532万
 $24,289/呎
-(17年-12月-27日)</t>
+(17年-12月-28日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -32065,7 +32065,7 @@
           <t>K | 293呎 (1房)
 $733万
 $25,021/呎
-(18年-06月-07日)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -32073,7 +32073,7 @@
           <t>L | 297呎 (1房)
 $730万
 $24,569/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -32081,7 +32081,7 @@
           <t>M | 214呎 (开放式)
 $539万
 $25,184/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -32089,7 +32089,7 @@
           <t>N | 216呎 (开放式)
 $554万
 $25,637/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -32097,7 +32097,7 @@
           <t>P | 384呎 (2房)
 $968万
 $25,210/呎
-(18年-04月-08日)</t>
+(18年-04月-09日)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr">
@@ -32105,7 +32105,7 @@
           <t>Q | 299呎 (1房)
 $769万
 $25,733/呎
-(20年-03月-26日)</t>
+(20年-03月-27日)</t>
         </is>
       </c>
       <c r="Q22" s="20" t="inlineStr">
@@ -32113,7 +32113,7 @@
           <t>R | 238呎 (开放式)
 $642万
 $26,957/呎
-(19年-07月-07日)</t>
+(19年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -32128,7 +32128,7 @@
           <t>A | 234呎 (开放式)
 $614万
 $26,240/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -32136,7 +32136,7 @@
           <t>B | 290呎 (1房)
 $756万
 $26,059/呎
-(19年-05月-21日)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -32144,7 +32144,7 @@
           <t>C | 293呎 (1房)
 $776万
 $26,493/呎
-(19年-04月-03日)</t>
+(19年-04月-04日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>D | 290呎 (1房)
 $705万
 $24,327/呎
-(17年-12月-13日)</t>
+(17年-12月-14日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -32160,7 +32160,7 @@
           <t>E | 300呎 (1房)
 $776万
 $25,853/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -32168,7 +32168,7 @@
           <t>F | 451呎 (2房)
 $1023万
 $22,685/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -32176,7 +32176,7 @@
           <t>G | 301呎 (1房)
 $764万
 $25,368/呎
-(19年-03月-05日)</t>
+(19年-03月-06日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -32184,7 +32184,7 @@
           <t>H | 290呎 (1房)
 $682万
 $23,527/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -32192,7 +32192,7 @@
           <t>J | 218呎 (开放式)
 $523万
 $23,981/呎
-(17年-12月-07日)</t>
+(17年-12月-08日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -32200,7 +32200,7 @@
           <t>K | 293呎 (1房)
 $728万
 $24,843/呎
-(18年-06月-14日)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -32208,7 +32208,7 @@
           <t>L | 297呎 (1房)
 $724万
 $24,391/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -32216,7 +32216,7 @@
           <t>M | 214呎 (开放式)
 $535万
 $25,005/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -32224,7 +32224,7 @@
           <t>N | 216呎 (开放式)
 $550万
 $25,456/呎
-(18年-05月-24日)</t>
+(18年-05月-25日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -32232,7 +32232,7 @@
           <t>P | 384呎 (2房)
 $961万
 $25,030/呎
-(18年-03月-19日)</t>
+(18年-03月-20日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -32240,7 +32240,7 @@
           <t>Q | 299呎 (1房)
 $769万
 $25,727/呎
-(20年-04月-08日)</t>
+(20年-04月-09日)</t>
         </is>
       </c>
       <c r="Q23" s="20" t="inlineStr">
@@ -32248,7 +32248,7 @@
           <t>R | 238呎 (开放式)
 $628万
 $26,396/呎
-(19年-05月-11日)</t>
+(19年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -32263,7 +32263,7 @@
           <t>A | 234呎 (开放式)
 $599万
 $25,597/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -32271,7 +32271,7 @@
           <t>B | 290呎 (1房)
 $745万
 $25,679/呎
-(19年-05月-21日)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32279,7 +32279,7 @@
           <t>C | 293呎 (1房)
 $765万
 $26,113/呎
-(19年-05月-29日)</t>
+(19年-05月-30日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -32287,7 +32287,7 @@
           <t>D | 290呎 (1房)
 $688万
 $23,732/呎
-(17年-11月-29日)</t>
+(17年-11月-30日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32295,7 +32295,7 @@
           <t>E | 299呎 (1房)
 $765万
 $25,570/呎
-(18年-06月-03日)</t>
+(18年-06月-04日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32303,7 +32303,7 @@
           <t>F | 451呎 (2房)
 $1016万
 $22,518/呎
-(17年-12月-12日)</t>
+(17年-12月-13日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -32311,7 +32311,7 @@
           <t>G | 301呎 (1房)
 $758万
 $25,183/呎
-(19年-03月-31日)</t>
+(19年-04月-01日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -32319,7 +32319,7 @@
           <t>H | 290呎 (1房)
 $677万
 $23,354/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -32327,7 +32327,7 @@
           <t>J | 219呎 (开放式)
 $530万
 $24,201/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -32335,7 +32335,7 @@
           <t>K | 293呎 (1房)
 $723万
 $24,668/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -32343,7 +32343,7 @@
           <t>L | 297呎 (1房)
 $719万
 $24,210/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -32351,7 +32351,7 @@
           <t>M | 214呎 (开放式)
 $526万
 $24,567/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -32359,7 +32359,7 @@
           <t>N | 216呎 (开放式)
 $552万
 $25,542/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -32367,7 +32367,7 @@
           <t>P | 384呎 (2房)
 $909万
 $23,665/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -32375,7 +32375,7 @@
           <t>Q | 299呎 (1房)
 $739万
 $24,722/呎
-(19年-06月-03日)</t>
+(19年-06月-04日)</t>
         </is>
       </c>
       <c r="Q24" s="20" t="inlineStr">
@@ -32383,7 +32383,7 @@
           <t>R | 238呎 (开放式)
 $617万
 $25,912/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -32398,7 +32398,7 @@
           <t>A | 234呎 (开放式)
 $590万
 $25,228/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -32406,7 +32406,7 @@
           <t>B | 290呎 (1房)
 $734万
 $25,299/呎
-(19年-01月-17日)</t>
+(19年-01月-18日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -32414,7 +32414,7 @@
           <t>C | 293呎 (1房)
 $754万
 $25,733/呎
-(19年-05月-09日)</t>
+(19年-05月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -32422,7 +32422,7 @@
           <t>D | 290呎 (1房)
 $722万
 $24,894/呎
-(18年-07月-20日)</t>
+(18年-07月-21日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32430,7 +32430,7 @@
           <t>E | 300呎 (1房)
 $756万
 $25,213/呎
-(18年-05月-15日)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32438,7 +32438,7 @@
           <t>F | 451呎 (2房)
 $1008万
 $22,355/呎
-(18年-01月-11日)</t>
+(18年-01月-12日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -32446,7 +32446,7 @@
           <t>G | 301呎 (1房)
 $745万
 $24,738/呎
-(19年-04月-03日)</t>
+(19年-04月-04日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -32454,7 +32454,7 @@
           <t>H | 290呎 (1房)
 $665万
 $22,944/呎
-(17年-12月-06日)</t>
+(17年-12月-07日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -32462,7 +32462,7 @@
           <t>J | 219呎 (开放式)
 $521万
 $23,781/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>K | 293呎 (1房)
 $725万
 $24,747/呎
-(18年-06月-03日)</t>
+(18年-06月-04日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>L | 297呎 (1房)
 $714万
 $24,032/呎
-(18年-05月-29日)</t>
+(18年-05月-30日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -32486,7 +32486,7 @@
           <t>M | 214呎 (开放式)
 $527万
 $24,646/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -32494,7 +32494,7 @@
           <t>N | 216呎 (开放式)
 $548万
 $25,360/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -32502,7 +32502,7 @@
           <t>P | 384呎 (2房)
 $947万
 $24,670/呎
-(18年-02月-25日)</t>
+(18年-02月-26日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -32510,7 +32510,7 @@
           <t>Q | 299呎 (1房)
 $725万
 $24,238/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="Q25" s="20" t="inlineStr">
@@ -32518,7 +32518,7 @@
           <t>R | 238呎 (开放式)
 $592万
 $24,888/呎
-(19年-05月-02日)</t>
+(19年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -32533,7 +32533,7 @@
           <t>A | 234呎 (开放式)
 $594万
 $25,382/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>B | 290呎 (1房)
 $723万
 $24,919/呎
-(18年-09月-19日)</t>
+(18年-09月-20日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32549,7 +32549,7 @@
           <t>C | 293呎 (1房)
 $743万
 $25,353/呎
-(19年-04月-28日)</t>
+(19年-04月-29日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -32557,7 +32557,7 @@
           <t>D | 290呎 (1房)
 $709万
 $24,454/呎
-(18年-07月-22日)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32565,7 +32565,7 @@
           <t>E | 300呎 (1房)
 $759万
 $25,286/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32573,7 +32573,7 @@
           <t>F | 451呎 (2房)
 $1040万
 $23,057/呎
-(18年-05月-08日)</t>
+(18年-05月-09日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -32581,7 +32581,7 @@
           <t>G | 301呎 (1房)
 $747万
 $24,813/呎
-(19年-04月-14日)</t>
+(19年-04月-15日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -32589,7 +32589,7 @@
           <t>H | 290呎 (1房)
 $681万
 $23,493/呎
-(17年-12月-07日)</t>
+(17年-12月-08日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -32597,7 +32597,7 @@
           <t>J | 218呎 (开放式)
 $512万
 $23,475/呎
-(17年-12月-13日)</t>
+(17年-12月-14日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -32605,7 +32605,7 @@
           <t>K | 293呎 (1房)
 $720万
 $24,570/呎
-(18年-05月-20日)</t>
+(18年-05月-21日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -32613,7 +32613,7 @@
           <t>L | 297呎 (1房)
 $708万
 $23,855/呎
-(18年-05月-02日)</t>
+(18年-05月-03日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr">
@@ -32621,7 +32621,7 @@
           <t>M | 214呎 (开放式)
 $518万
 $24,212/呎
-(18年-05月-20日)</t>
+(18年-05月-21日)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -32629,7 +32629,7 @@
           <t>N | 216呎 (开放式)
 $538万
 $24,916/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="O26" s="20" t="inlineStr">
@@ -32637,7 +32637,7 @@
           <t>P | 384呎 (2房)
 $950万
 $24,743/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="P26" s="20" t="inlineStr">
@@ -32645,7 +32645,7 @@
           <t>Q | 299呎 (1房)
 $706万
 $23,620/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
       <c r="Q26" s="20" t="inlineStr">
@@ -32653,7 +32653,7 @@
           <t>R | 238呎 (开放式)
 $583万
 $24,512/呎
-(19年-05月-19日)</t>
+(19年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -32668,7 +32668,7 @@
           <t>A | 234呎 (开放式)
 $575万
 $24,582/呎
-(18年-08月-22日)</t>
+(18年-08月-23日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -32676,7 +32676,7 @@
           <t>B | 290呎 (1房)
 $722万
 $24,897/呎
-(18年-09月-23日)</t>
+(18年-09月-24日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -32684,7 +32684,7 @@
           <t>C | 293呎 (1房)
 $734万
 $25,068/呎
-(18年-12月-03日)</t>
+(18年-12月-04日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -32692,7 +32692,7 @@
           <t>D | 290呎 (1房)
 $711万
 $24,530/呎
-(18年-08月-08日)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -32700,7 +32700,7 @@
           <t>E | 300呎 (1房)
 $745万
 $24,839/呎
-(19年-04月-09日)</t>
+(19年-04月-10日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -32708,7 +32708,7 @@
           <t>F | 451呎 (2房)
 $1032万
 $22,886/呎
-(18年-05月-10日)</t>
+(18年-05月-11日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -32716,7 +32716,7 @@
           <t>G | 301呎 (1房)
 $734万
 $24,372/呎
-(19年-03月-31日)</t>
+(19年-04月-01日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -32724,7 +32724,7 @@
           <t>H | 290呎 (1房)
 $656万
 $22,607/呎
-(17年-12月-27日)</t>
+(17年-12月-28日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -32732,7 +32732,7 @@
           <t>J | 219呎 (开放式)
 $508万
 $23,199/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -32740,7 +32740,7 @@
           <t>K | 293呎 (1房)
 $715万
 $24,390/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -32748,7 +32748,7 @@
           <t>L | 297呎 (1房)
 $703万
 $23,677/呎
-(18年-04月-27日)</t>
+(18年-04月-28日)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
@@ -32756,7 +32756,7 @@
           <t>M | 214呎 (开放式)
 $514万
 $24,039/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -32764,7 +32764,7 @@
           <t>N | 216呎 (开放式)
 $540万
 $24,996/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="O27" s="20" t="inlineStr">
@@ -32772,7 +32772,7 @@
           <t>P | 384呎 (2房)
 $933万
 $24,308/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="P27" s="20" t="inlineStr">
@@ -32780,7 +32780,7 @@
           <t>Q | 299呎 (1房)
 $705万
 $23,589/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="Q27" s="20" t="inlineStr">
@@ -32788,7 +32788,7 @@
           <t>R | 238呎 (开放式)
 $583万
 $24,484/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -32803,7 +32803,7 @@
           <t>A | 234呎 (开放式)
 $569万
 $24,306/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -32811,7 +32811,7 @@
           <t>B | 290呎 (1房)
 $706万
 $24,353/呎
-(18年-09月-19日)</t>
+(18年-09月-20日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -32819,7 +32819,7 @@
           <t>C | 293呎 (1房)
 $719万
 $24,528/呎
-(18年-10月-03日)</t>
+(18年-10月-04日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -32827,7 +32827,7 @@
           <t>D | 290呎 (1房)
 $706万
 $24,344/呎
-(18年-07月-23日)</t>
+(18年-07月-24日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -32835,7 +32835,7 @@
           <t>E | 300呎 (1房)
 $740万
 $24,659/呎
-(18年-08月-30日)</t>
+(18年-08月-31日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -32843,7 +32843,7 @@
           <t>F | 451呎 (2房)
 $976万
 $21,635/呎
-(18年-02月-11日)</t>
+(18年-02月-12日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -32851,7 +32851,7 @@
           <t>G | 301呎 (1房)
 $736万
 $24,443/呎
-(19年-02月-26日)</t>
+(19年-02月-27日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -32859,7 +32859,7 @@
           <t>H | 290呎 (1房)
 $671万
 $23,145/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -32867,7 +32867,7 @@
           <t>J | 219呎 (开放式)
 $504万
 $23,030/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -32875,7 +32875,7 @@
           <t>K | 293呎 (1房)
 $702万
 $23,958/呎
-(18年-06月-13日)</t>
+(18年-06月-14日)</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -32883,7 +32883,7 @@
           <t>L | 297呎 (1房)
 $698万
 $23,496/呎
-(18年-05月-23日)</t>
+(18年-05月-24日)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr">
@@ -32891,7 +32891,7 @@
           <t>M | 214呎 (开放式)
 $527万
 $24,614/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -32899,7 +32899,7 @@
           <t>N | 216呎 (开放式)
 $530万
 $24,555/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="O28" s="20" t="inlineStr">
@@ -32907,7 +32907,7 @@
           <t>P | 384呎 (2房)
 $917万
 $23,876/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="P28" s="20" t="inlineStr">
@@ -32915,7 +32915,7 @@
           <t>Q | 299呎 (1房)
 $697万
 $23,310/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="Q28" s="20" t="inlineStr">
@@ -32923,7 +32923,7 @@
           <t>R | 238呎 (开放式)
 $570万
 $23,950/呎
-(19年-05月-21日)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -32938,7 +32938,7 @@
           <t>A | 234呎 (开放式)
 $567万
 $24,213/呎
-(18年-08月-22日)</t>
+(18年-08月-23日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -32946,7 +32946,7 @@
           <t>B | 290呎 (1房)
 $711万
 $24,513/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -32954,7 +32954,7 @@
           <t>C | 293呎 (1房)
 $723万
 $24,691/呎
-(18年-10月-02日)</t>
+(18年-10月-03日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -32962,7 +32962,7 @@
           <t>D | 290呎 (1房)
 $711万
 $24,508/呎
-(18年-08月-08日)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -32970,7 +32970,7 @@
           <t>E | 300呎 (1房)
 $737万
 $24,567/呎
-(18年-08月-27日)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -32978,7 +32978,7 @@
           <t>F | 451呎 (2房)
 $982万
 $21,780/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -32986,7 +32986,7 @@
           <t>G | 301呎 (1房)
 $733万
 $24,351/呎
-(19年-02月-26日)</t>
+(19年-02月-27日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -32994,7 +32994,7 @@
           <t>H | 290呎 (1房)
 $655万
 $22,586/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -33002,7 +33002,7 @@
           <t>J | 219呎 (开放式)
 $503万
 $22,947/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -33010,7 +33010,7 @@
           <t>K | 293呎 (1房)
 $727万
 $24,801/呎
-(19年-04月-07日)</t>
+(19年-04月-08日)</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -33018,7 +33018,7 @@
           <t>L | 297呎 (1房)
 $721万
 $24,268/呎
-(19年-03月-13日)</t>
+(19年-03月-14日)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr">
@@ -33026,7 +33026,7 @@
           <t>M | 214呎 (开放式)
 $544万
 $25,429/呎
-(18年-10月-03日)</t>
+(18年-10月-04日)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -33034,7 +33034,7 @@
           <t>N | 216呎 (开放式)
 $538万
 $24,920/呎
-(18年-09月-25日)</t>
+(18年-09月-26日)</t>
         </is>
       </c>
       <c r="O29" s="20" t="inlineStr">
@@ -33042,7 +33042,7 @@
           <t>P | 384呎 (2房)
 $913万
 $23,787/呎
-(18年-07月-22日)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
       <c r="P29" s="20" t="inlineStr">
@@ -33050,7 +33050,7 @@
           <t>Q | 299呎 (1房)
 $689万
 $23,030/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="Q29" s="20" t="inlineStr">
@@ -33058,7 +33058,7 @@
           <t>R | 238呎 (开放式)
 $569万
 $23,915/呎
-(19年-06月-02日)</t>
+(19年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -33073,7 +33073,7 @@
           <t>A | 234呎 (开放式)
 $576万
 $24,627/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -33081,7 +33081,7 @@
           <t>B | 290呎 (1房)
 $708万
 $24,417/呎
-(18年-09月-25日)</t>
+(18年-09月-26日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -33089,7 +33089,7 @@
           <t>C | 293呎 (1房)
 $721万
 $24,596/呎
-(19年-03月-17日)</t>
+(19年-03月-18日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -33097,7 +33097,7 @@
           <t>D | 290呎 (1房)
 $701万
 $24,162/呎
-(18年-08月-08日)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -33105,7 +33105,7 @@
           <t>E | 300呎 (1房)
 $750万
 $24,990/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -33113,7 +33113,7 @@
           <t>F | 451呎 (2房)
 $1009万
 $22,377/呎
-(18年-04月-10日)</t>
+(18年-04月-11日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -33121,7 +33121,7 @@
           <t>G | 301呎 (1房)
 $725万
 $24,073/呎
-(19年-03月-31日)</t>
+(19年-04月-01日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -33129,7 +33129,7 @@
           <t>H | 290呎 (1房)
 $641万
 $22,099/呎
-(17年-12月-12日)</t>
+(17年-12月-13日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -33137,7 +33137,7 @@
           <t>J | 219呎 (开放式)
 $502万
 $22,935/呎
-(17年-12月-10日)</t>
+(17年-12月-11日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -33145,7 +33145,7 @@
           <t>K | 293呎 (1房)
 $712万
 $24,295/呎
-(19年-02月-11日)</t>
+(19年-02月-12日)</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
@@ -33153,7 +33153,7 @@
           <t>L | 297呎 (1房)
 $734万
 $24,727/呎
-(19年-04月-16日)</t>
+(19年-04月-17日)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr">
@@ -33161,7 +33161,7 @@
           <t>M | 214呎 (开放式)
 $527万
 $24,625/呎
-(18年-09月-27日)</t>
+(18年-09月-28日)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -33169,7 +33169,7 @@
           <t>N | 216呎 (开放式)
 $543万
 $25,162/呎
-(18年-09月-25日)</t>
+(18年-09月-26日)</t>
         </is>
       </c>
       <c r="O30" s="20" t="inlineStr">
@@ -33177,7 +33177,7 @@
           <t>P | 384呎 (2房)
 $875万
 $22,782/呎
-(17年-11月-30日)</t>
+(17年-12月-01日)</t>
         </is>
       </c>
       <c r="P30" s="20" t="inlineStr">
@@ -33185,7 +33185,7 @@
           <t>Q | 299呎 (1房)
 $680万
 $22,751/呎
-(19年-05月-15日)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
       <c r="Q30" s="20" t="inlineStr">
@@ -33193,7 +33193,7 @@
           <t>R | 238呎 (开放式)
 $557万
 $23,383/呎
-(19年-05月-20日)</t>
+(19年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -33208,7 +33208,7 @@
           <t>A | 234呎 (开放式)
 $570万
 $24,373/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -33216,7 +33216,7 @@
           <t>B | 290呎 (1房)
 $701万
 $24,163/呎
-(18年-09月-17日)</t>
+(18年-09月-18日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -33224,7 +33224,7 @@
           <t>C | 293呎 (1房)
 $713万
 $24,340/呎
-(19年-04月-11日)</t>
+(19年-04月-12日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -33232,7 +33232,7 @@
           <t>D | 290呎 (1房)
 $708万
 $24,414/呎
-(18年-07月-23日)</t>
+(18年-07月-24日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -33240,7 +33240,7 @@
           <t>E | 300呎 (1房)
 $734万
 $24,475/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -33248,7 +33248,7 @@
           <t>F | 451呎 (2房)
 $1008万
 $22,352/呎
-(18年-03月-19日)</t>
+(18年-03月-20日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -33256,7 +33256,7 @@
           <t>G | 301呎 (1房)
 $716万
 $23,796/呎
-(19年-04月-14日)</t>
+(19年-04月-15日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -33264,7 +33264,7 @@
           <t>H | 290呎 (1房)
 $640万
 $22,077/呎
-(17年-12月-20日)</t>
+(17年-12月-21日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -33272,7 +33272,7 @@
           <t>J | 219呎 (开放式)
 $492万
 $22,444/呎
-(17年-12月-06日)</t>
+(17年-12月-07日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -33280,7 +33280,7 @@
           <t>K | 293呎 (1房)
 $718万
 $24,505/呎
-(19年-03月-26日)</t>
+(19年-03月-27日)</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -33288,7 +33288,7 @@
           <t>L | 297呎 (1房)
 $704万
 $23,712/呎
-(19年-01月-22日)</t>
+(19年-01月-23日)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr">
@@ -33296,7 +33296,7 @@
           <t>M | 214呎 (开放式)
 $532万
 $24,862/呎
-(18年-10月-03日)</t>
+(18年-10月-04日)</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -33304,7 +33304,7 @@
           <t>N | 216呎 (开放式)
 $532万
 $24,627/呎
-(18年-09月-25日)</t>
+(18年-09月-26日)</t>
         </is>
       </c>
       <c r="O31" s="20" t="inlineStr">
@@ -33312,7 +33312,7 @@
           <t>P | 384呎 (2房)
 $886万
 $23,072/呎
-(18年-05月-27日)</t>
+(18年-05月-28日)</t>
         </is>
       </c>
       <c r="P31" s="20" t="inlineStr">
@@ -33320,7 +33320,7 @@
           <t>Q | 299呎 (1房)
 $665万
 $22,238/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
       <c r="Q31" s="20" t="inlineStr">
@@ -33328,7 +33328,7 @@
           <t>R | 238呎 (开放式)
 $550万
 $23,099/呎
-(19年-05月-30日)</t>
+(19年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -33343,7 +33343,7 @@
           <t>A | 234呎 (开放式)
 $579万
 $24,723/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -33351,7 +33351,7 @@
           <t>B | 290呎 (1房)
 $711万
 $24,513/呎
-(18年-09月-23日)</t>
+(18年-09月-24日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -33359,7 +33359,7 @@
           <t>C | 293呎 (1房)
 $723万
 $24,691/呎
-(19年-04月-23日)</t>
+(19年-04月-24日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -33367,7 +33367,7 @@
           <t>D | 290呎 (1房)
 $703万
 $24,255/呎
-(18年-08月-08日)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -33375,7 +33375,7 @@
           <t>E | 299呎 (1房)
 $753万
 $25,168/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -33383,7 +33383,7 @@
           <t>F | 451呎 (2房)
 $947万
 $21,003/呎
-(18年-02月-11日)</t>
+(18年-02月-12日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -33391,7 +33391,7 @@
           <t>G | 301呎 (1房)
 $708万
 $23,522/呎
-(19年-03月-05日)</t>
+(19年-03月-06日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -33399,7 +33399,7 @@
           <t>H | 290呎 (1房)
 $626万
 $21,591/呎
-(18年-01月-16日)</t>
+(18年-01月-17日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -33407,7 +33407,7 @@
           <t>J | 218呎 (开放式)
 $486万
 $22,294/呎
-(17年-12月-14日)</t>
+(17年-12月-15日)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -33415,7 +33415,7 @@
           <t>K | 293呎 (1房)
 $689万
 $23,500/呎
-(19年-01月-29日)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">
@@ -33423,7 +33423,7 @@
           <t>L | 297呎 (1房)
 $717万
 $24,155/呎
-(19年-04月-02日)</t>
+(19年-04月-03日)</t>
         </is>
       </c>
       <c r="M32" s="20" t="inlineStr">
@@ -33431,7 +33431,7 @@
           <t>M | 214呎 (开放式)
 $521万
 $24,323/呎
-(18年-10月-04日)</t>
+(18年-10月-05日)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -33439,7 +33439,7 @@
           <t>N | 216呎 (开放式)
 $531万
 $24,600/呎
-(18年-10月-08日)</t>
+(18年-10月-09日)</t>
         </is>
       </c>
       <c r="O32" s="20" t="inlineStr">
@@ -33447,7 +33447,7 @@
           <t>P | 384呎 (2房)
 $881万
 $22,952/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="P32" s="20" t="inlineStr">
@@ -33455,7 +33455,7 @@
           <t>Q | 299呎 (1房)
 $657万
 $21,964/呎
-(19年-05月-16日)</t>
+(19年-05月-17日)</t>
         </is>
       </c>
       <c r="Q32" s="20" t="inlineStr">
@@ -33463,7 +33463,7 @@
           <t>R | 238呎 (开放式)
 $543万
 $22,820/呎
-(19年-05月-26日)</t>
+(19年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -33478,7 +33478,7 @@
           <t>A | 213呎 (开放式)
 $706万
 $33,138/呎
-(20年-02月-05日)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -33486,7 +33486,7 @@
           <t>B | 251呎 (1房)
 $748万
 $29,817/呎
-(19年-11月-17日)</t>
+(19年-11月-18日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -33494,7 +33494,7 @@
           <t>C | 255呎 (1房)
 $770万
 $30,182/呎
-(19年-12月-05日)</t>
+(19年-12月-06日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -33502,7 +33502,7 @@
           <t>D | 252呎 (1房)
 $787万
 $31,234/呎
-(20年-01月-08日)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -33510,7 +33510,7 @@
           <t>E | 262呎 (1房)
 $868万
 $33,124/呎
-(20年-07月-12日)</t>
+(20年-07月-13日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -33518,7 +33518,7 @@
           <t>F | 412呎 (2房)
 $1232万
 $29,904/呎
-(19年-10月-15日)</t>
+(19年-10月-16日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -33526,7 +33526,7 @@
           <t>G | 263呎 (1房)
 $817万
 $31,079/呎
-(19年-10月-24日)</t>
+(19年-10月-25日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -33534,7 +33534,7 @@
           <t>H | 251呎 (1房)
 $768万
 $30,608/呎
-(19年-09月-23日)</t>
+(19年-09月-24日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -33542,7 +33542,7 @@
           <t>J | 197呎 (开放式)
 $615万
 $31,212/呎
-(19年-10月-07日)</t>
+(19年-10月-08日)</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
@@ -33550,7 +33550,7 @@
           <t>K | 255呎 (1房)
 $808万
 $31,699/呎
-(19年-07月-28日)</t>
+(19年-07月-29日)</t>
         </is>
       </c>
       <c r="L33" s="20" t="inlineStr">
@@ -33558,7 +33558,7 @@
           <t>L | 259呎 (1房)
 $815万
 $31,458/呎
-(19年-08月-15日)</t>
+(19年-08月-16日)</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>M | 193呎 (开放式)
 $619万
 $32,098/呎
-(19年-08月-15日)</t>
+(19年-08月-16日)</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>N | 195呎 (开放式)
 $608万
 $31,198/呎
-(19年-08月-11日)</t>
+(19年-08月-12日)</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>P | 344呎 (2房)
 $1036万
 $30,116/呎
-(19年-10月-24日)</t>
+(19年-10月-25日)</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr">
@@ -33590,7 +33590,7 @@
           <t>Q | 263呎 (1房)
 $776万
 $29,494/呎
-(19年-06月-05日)</t>
+(19年-06月-06日)</t>
         </is>
       </c>
       <c r="Q33" s="20" t="inlineStr">
@@ -33598,7 +33598,7 @@
           <t>R | 216呎 (开放式)
 $606万
 $28,069/呎
-(19年-05月-21日)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/web/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -6268,34 +6268,34 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>7463000</v>
+        <v>7089800</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>24794</v>
+        <v>23554</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>7089850</v>
+        <v>7089800</v>
       </c>
       <c r="L92" s="5" t="n">
         <v>23554</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>現金或即時按揭付款計劃 - 120天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>456</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30416,12 +30416,12 @@
 (18年-05月-16日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
-$746万
-$24,794/呎
-(在售)</t>
+$709万
+$23,554/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">

--- a/web/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/web/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -29142,7 +29142,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>12320550</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>29904</v>
+        <v>29832</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>12320550</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>29904</v>
+        <v>29832</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -33515,9 +33515,9 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>F | 412呎 (2房)
+          <t>F | 413呎 (2房)
 $1232万
-$29,904/呎
+$29,832/呎
 (19年-10月-16日)</t>
         </is>
       </c>

--- a/web/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/web/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -6273,7 +6273,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -30421,7 +30421,7 @@
           <t>G | 301呎 (1房)
 $709万
 $23,554/呎
-(26年-08月-03日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
